--- a/artfynd/A 38832-2026 artfynd.xlsx
+++ b/artfynd/A 38832-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,62 +680,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127878412</v>
+        <v>136856460</v>
       </c>
       <c r="B2" t="n">
-        <v>56845</v>
+        <v>75566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100053</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stengårdevägen, 622 66 Gotlands kommun, Gtl</t>
+          <t>Smågårde, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687766</v>
+        <v>687725</v>
       </c>
       <c r="R2" t="n">
-        <v>6377434</v>
+        <v>6377794</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20:40</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>20:40</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,34 +766,610 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136856460</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136856474</v>
+      </c>
+      <c r="B3" t="n">
+        <v>75566</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Smågårde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>687760</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6377672</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136856474</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136856538</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75566</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smågårde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>687722</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6377631</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136856538</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136856427</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Smågårde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>687747</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6377754</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136856427</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127878412</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stengårdevägen, 622 66 Gotlands kommun, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>687766</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6377434</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Johan Möller</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Via Johan Möller</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127878412</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136856507</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58283</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Smågårde, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>687760</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6377672</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136856507</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38832-2026 artfynd.xlsx
+++ b/artfynd/A 38832-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136856460</v>
       </c>
       <c r="B2" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136856474</v>
       </c>
       <c r="B3" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136856538</v>
       </c>
       <c r="B4" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136856427</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136856507</v>
       </c>
       <c r="B7" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38832-2026 artfynd.xlsx
+++ b/artfynd/A 38832-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136856460</v>
       </c>
       <c r="B2" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136856474</v>
       </c>
       <c r="B3" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136856538</v>
       </c>
       <c r="B4" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136856427</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136856507</v>
       </c>
       <c r="B7" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38832-2026 artfynd.xlsx
+++ b/artfynd/A 38832-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -820,11 +816,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -930,11 +922,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1045,11 +1033,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 38832-2026 artfynd.xlsx
+++ b/artfynd/A 38832-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136856460</v>
       </c>
       <c r="B2" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856474</v>
       </c>
       <c r="B3" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136856538</v>
       </c>
       <c r="B4" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136856427</v>
       </c>
       <c r="B5" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136856507</v>
       </c>
       <c r="B7" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38832-2026 artfynd.xlsx
+++ b/artfynd/A 38832-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136856460</v>
       </c>
       <c r="B2" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856474</v>
       </c>
       <c r="B3" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136856538</v>
       </c>
       <c r="B4" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136856427</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136856507</v>
       </c>
       <c r="B7" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38832-2026 artfynd.xlsx
+++ b/artfynd/A 38832-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136856460</v>
       </c>
       <c r="B2" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856474</v>
       </c>
       <c r="B3" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136856538</v>
       </c>
       <c r="B4" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136856427</v>
       </c>
       <c r="B5" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136856507</v>
       </c>
       <c r="B7" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38832-2026 artfynd.xlsx
+++ b/artfynd/A 38832-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136856460</v>
       </c>
       <c r="B2" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136856474</v>
       </c>
       <c r="B3" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136856538</v>
       </c>
       <c r="B4" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
